--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_tarapaca.xlsx
@@ -375,46 +375,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="C2">
-        <v>150333</v>
+        <v>90.85963003264418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C3">
-        <v>102616</v>
+        <v>90.68033550792171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C4">
-        <v>13250</v>
+        <v>86.36183839556981</v>
       </c>
     </row>
     <row r="5">
@@ -429,37 +429,37 @@
         </is>
       </c>
       <c r="C5">
-        <v>5308</v>
+        <v>85.13231756214915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Pozo Almonte</t>
         </is>
       </c>
       <c r="C6">
-        <v>2505</v>
+        <v>83.80241603946619</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camiña</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C7">
-        <v>973</v>
+        <v>72.4583684781299</v>
       </c>
     </row>
   </sheetData>
@@ -515,7 +515,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -460,6 +460,2976 @@
       </c>
       <c r="C7">
         <v>72.4583684781299</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>47.80987884436161</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>45.95574900253899</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>44.90388103010519</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>44.20935693185548</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>43.62469927826784</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>42.87045666356011</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>42.48308139902599</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>42.15248146371432</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>41.93849021435229</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>41.50761828388131</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>41.3193346404402</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>37.89757802144837</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>36.38012332245194</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>34.56079045668153</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>30.38210624417521</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>28.50924918389554</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>28.50040096230954</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>28.20484395710326</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>27.43286119456998</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>26.21422139184151</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>24.58700882117081</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>24.31851242805642</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>23.5342483081399</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>22.28828031117576</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>21.90787087413856</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>20.89697949015746</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>20.1304753028891</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>19.21630014896357</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>19.06267788248688</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>18.88179298710688</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>18.68484362469928</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>18.26533317267141</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>17.73857257417803</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>16.58900279589935</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>16.03191875226696</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>15.44171484838539</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>15.08886470801596</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>14.66154972605852</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>14.35228331780056</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>13.66137499209411</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>13.61668003207699</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>13.57030967586456</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>13.52855606855986</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>13.49845566019475</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>13.36006415396953</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>13.34402566158781</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>13.30184359561393</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>13.13642400860161</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>13.09394269133116</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>12.803772216177</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>12.35618749246897</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>12.20876048462255</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>12.17321571772253</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>12.10055461576657</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>12.06988793830582</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>11.68174056036936</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>11.27679403541472</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>10.90010844680082</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>10.48240841494378</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>10.3448275862069</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>10.2503916134474</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>10.15843429636533</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>10.09333366997416</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>9.938338774029743</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>9.861429087841909</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>9.360571753842262</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>9.226467847157503</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>9.17026147728642</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>9.029671210906175</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>8.946877912395154</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>8.922742110990207</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>8.88532477947073</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>8.822971349060781</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>8.560029017047516</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>8.552837691288106</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>8.452285485164394</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>8.209474416545444</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>8.047234606579106</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>8.014941559224003</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>7.723382230413816</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>7.364018144940709</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>6.925558155714376</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>6.150978564771668</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>5.765031931558019</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>5.444323814813879</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>5.212510024057739</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>4.786190993174607</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>4.408323319208146</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>4.155199421617063</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>3.778768526328473</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>3.393179901192915</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>3.372936498373298</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>3.239775461106656</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>2.964694541511026</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>2.924207735871792</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>2.730157127107161</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>2.577827151766102</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>2.51723483650623</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>2.466449038810301</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>2.389735364875702</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>2.335703096758646</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>2.331365224725871</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>2.294252319556573</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>2.150401619125925</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>1.924619085805934</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>1.876852632847331</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>1.853140218834988</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>1.844426623897354</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>1.754740323680158</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>1.647856860319304</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>1.584342963653308</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>1.54433980525328</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>1.543229397255076</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>1.524982957558007</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>1.523394994559303</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>1.511605844032635</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>1.491579791499599</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>1.491579791499599</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>1.442034026943267</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>1.411387329591018</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>1.340838656631459</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>1.276710345814292</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>1.117647553883573</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>1.106655974338412</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>1.027596131996869</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>1.016508013013616</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>0.9943865276663993</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>0.9623095429029671</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>0.9569015578054384</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>0.9430540442509975</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>0.9319664492078286</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>0.9297324647397381</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>0.8981555733761026</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>0.8660785886126704</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>0.7979688066739209</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>0.7858861267040899</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>0.7463158560495857</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>0.7336664347606097</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>0.6891548784911136</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>0.6523765144454799</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>0.6166122597025753</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>0.6094627105052125</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>0.6071722218708494</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>0.5692239580039213</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>0.5591798695246971</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>0.523476489846071</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>0.4659832246039143</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>0.4628811405391303</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>0.4352557127312296</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>0.3727865796831314</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>0.3727865796831314</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>0.3627130939426914</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>0.3627130939426914</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>0.3264417845484222</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>0.3264417845484222</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>0.3264417845484222</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>0.3264417845484222</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>0.2846119790019607</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>0.2795899347623486</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>0.2795899347623486</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>0.2795899347623486</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>0.2538991657598839</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>0.1863932898415657</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>0.1863932898415657</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>0.1863932898415657</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>0.1542354500542234</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>0.1142306301964092</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>0.1122694466720128</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>0.1088139281828074</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>0.09487065966732022</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>0.09257622810782606</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>0.04819857814194482</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>0.03955529746425295</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>0.01897413193346404</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>0.01897413193346404</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>0.01603849238171612</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>0.01599043940044268</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>0.007574418663367587</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>0.006324710644488015</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>0.005301843595613929</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>0.005049612442245058</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
